--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488228_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488228_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.683999999999999</v>
+        <v>8.179600000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.284</v>
+        <v>6.0997</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.0799</v>
       </c>
       <c r="G2" t="n">
         <v>5.2032</v>
@@ -610,13 +610,13 @@
         <v>1.4823</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3696</v>
+        <v>0.8652</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4179</v>
+        <v>0.2335</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9518</v>
+        <v>0.6317</v>
       </c>
       <c r="V2" t="n">
         <v>0.6289</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.7829</v>
+        <v>6.9547</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9838</v>
+        <v>4.0817</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7992</v>
+        <v>2.873</v>
       </c>
       <c r="G3" t="n">
         <v>7.2927</v>
@@ -688,13 +688,13 @@
         <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0281</v>
+        <v>0.1999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4203</v>
+        <v>-0.3224</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4484</v>
+        <v>0.5223</v>
       </c>
       <c r="V3" t="n">
         <v>0.9444</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9443</v>
+        <v>1.9503</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2847</v>
+        <v>3.2415</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3404</v>
+        <v>-1.2912</v>
       </c>
       <c r="G4" t="n">
         <v>3.7749</v>
@@ -766,13 +766,13 @@
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2604</v>
+        <v>0.2664</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0501</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1671</v>
+        <v>0.2164</v>
       </c>
       <c r="V4" t="n">
         <v>-2.8321</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1097</v>
+        <v>0.974</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.0184</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0416</v>
+        <v>1.9924</v>
       </c>
       <c r="G5" t="n">
         <v>-1.6229</v>
@@ -844,13 +844,13 @@
         <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9359</v>
+        <v>0.8002</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2873</v>
+        <v>0.2009</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6486</v>
+        <v>0.5994</v>
       </c>
       <c r="V5" t="n">
         <v>0.3144</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. BENÍTEZ SIERRA</t>
+          <t>C. CORRALES GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6221</v>
+        <v>0.7385</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6221</v>
+        <v>-0.5585</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6221</v>
+        <v>0.2365</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.3256</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6221</v>
+        <v>-0.0891</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6221</v>
+        <v>-0.547</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0644</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6221</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.7834</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.2611</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.5223</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.0538</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.0115</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.0423</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. PEREZ SAENZ</t>
+          <t>F. BENÍTEZ SIERRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5613</v>
+        <v>0.6221</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1641</v>
+        <v>0.6221</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7255</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1306</v>
+        <v>0.6221</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1306</v>
+        <v>0.6221</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.6221</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6221</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1306</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1306</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0602</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1641</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2243</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. CORRALES GARCIA</t>
+          <t>I. PEREZ SAENZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5421</v>
+        <v>0.4875</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6564</v>
+        <v>-0.1641</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1985</v>
+        <v>0.6516</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2365</v>
+        <v>0.1306</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3256</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0891</v>
+        <v>0.1306</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.547</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0644</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7834</v>
+        <v>0.1306</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2611</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5223</v>
+        <v>0.1306</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2502</v>
+        <v>-0.0137</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1094</v>
+        <v>-0.1641</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1408</v>
+        <v>0.1505</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>D. PAVON CRUZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3905</v>
+        <v>0.1579</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1921</v>
+        <v>-0.0547</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5826</v>
+        <v>0.2126</v>
       </c>
       <c r="G10" t="n">
-        <v>0.19</v>
+        <v>0.1306</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2233</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4133</v>
+        <v>0.1306</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1676</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9971</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8294</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3576</v>
+        <v>0.1306</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2263</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5839</v>
+        <v>0.1306</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0147</v>
+        <v>0.0274</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1716</v>
+        <v>-0.0547</v>
       </c>
       <c r="U10" t="n">
-        <v>1.1863</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3549</v>
+        <v>0.1109</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-1.0263</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9895</v>
+        <v>1.1372</v>
       </c>
       <c r="G11" t="n">
         <v>1.1617</v>
@@ -1312,13 +1312,13 @@
         <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.3096</v>
       </c>
       <c r="T11" t="n">
-        <v>0.434</v>
+        <v>0.0423</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4997</v>
+        <v>-0.3519</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. PAVON CRUZ</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1087</v>
+        <v>0.0032</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0547</v>
+        <v>-2.3332</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1634</v>
+        <v>2.3364</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1306</v>
+        <v>0.19</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-1.2233</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1306</v>
+        <v>1.4133</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.1676</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.9971</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.8294</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1306</v>
+        <v>0.3576</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-0.2263</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1306</v>
+        <v>0.5839</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0219</v>
+        <v>0.6274</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0547</v>
+        <v>-0.3127</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0328</v>
+        <v>0.9401</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4597</v>
+        <v>-2.1593</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0571</v>
+        <v>-2.9044</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5974</v>
+        <v>0.7451</v>
       </c>
       <c r="G13" t="n">
         <v>-1.612</v>
@@ -1468,13 +1468,13 @@
         <v>0.9264</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5332</v>
+        <v>-0.2329</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4166</v>
+        <v>-0.2639</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1167</v>
+        <v>0.0311</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3144</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.573</v>
+        <v>-2.8317</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.7448</v>
+        <v>-3.2005</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1718</v>
+        <v>0.3688</v>
       </c>
       <c r="G14" t="n">
         <v>-2.1522</v>
@@ -1546,13 +1546,13 @@
         <v>1.297</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2181</v>
+        <v>0.5232</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.3099</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6362</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5733</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.267</v>
+        <v>-3.8397</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.3672</v>
+        <v>-2.866</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8998</v>
+        <v>-0.9736</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2163</v>
@@ -1624,13 +1624,13 @@
         <v>1.1117</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1798</v>
+        <v>0.2475</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6143</v>
+        <v>-0.1131</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4345</v>
+        <v>0.3606</v>
       </c>
       <c r="V15" t="n">
         <v>-2.2033</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>11.74489999999999</v>
+        <v>12.2921</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3156999999999979</v>
+        <v>0.8629999999999982</v>
       </c>
       <c r="F16" t="n">
-        <v>11.4293</v>
+        <v>11.4292</v>
       </c>
       <c r="G16" t="n">
         <v>14.083</v>
@@ -1702,13 +1702,13 @@
         <v>13.8965</v>
       </c>
       <c r="S16" t="n">
-        <v>2.399999999999999</v>
+        <v>2.9472</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.5728</v>
+        <v>-1.0255</v>
       </c>
       <c r="U16" t="n">
-        <v>3.9728</v>
+        <v>3.9732</v>
       </c>
       <c r="V16" t="n">
         <v>-5.6643</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1762</v>
+        <v>1.7455</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0308</v>
+        <v>0.7526</v>
       </c>
       <c r="F17" t="n">
-        <v>1.207</v>
+        <v>0.9929</v>
       </c>
       <c r="G17" t="n">
         <v>-2.9053</v>
@@ -1780,13 +1780,13 @@
         <v>1.8529</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6389</v>
+        <v>-0.0696</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4773</v>
+        <v>-0.6939</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8384</v>
+        <v>0.6242</v>
       </c>
       <c r="V17" t="n">
         <v>4.7204</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>S. VICENTE GARCÍA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0319</v>
+        <v>0.3221</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2596</v>
+        <v>0.3221</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5986</v>
+        <v>0.3221</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8002</v>
+        <v>0.3221</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2016</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0052</v>
+        <v>0.3221</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8808</v>
+        <v>0.3221</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1244</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6038</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.681</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0772</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.631</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3493</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2818</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCÍA</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3221</v>
+        <v>0.2337</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3221</v>
+        <v>-0.6167</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.8504</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3221</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3221</v>
+        <v>1.4745</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1.4084</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3221</v>
+        <v>2.3251</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3221</v>
+        <v>4.1178</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.7927</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-2.2589</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-2.6433</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.3843</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-4.8175</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.594</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.4411</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.9559</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.5148</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.8321</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.8316</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0707</v>
+        <v>0.0059</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.2092</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0139</v>
+        <v>0.2152</v>
       </c>
       <c r="G20" t="n">
         <v>-0.429</v>
@@ -2014,13 +2014,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1291</v>
+        <v>0.0644</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2699</v>
+        <v>-0.0239</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1408</v>
+        <v>0.0883</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>D. PENAS REINO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3362</v>
+        <v>-0.1556</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3022</v>
+        <v>-0.0002</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9661</v>
+        <v>-0.1554</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.4062</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4745</v>
+        <v>-0.2095</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4084</v>
+        <v>-0.1967</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3251</v>
+        <v>0.0228</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1178</v>
+        <v>0.0429</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7927</v>
+        <v>-0.0201</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2589</v>
+        <v>-0.429</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.6433</v>
+        <v>-0.2524</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3843</v>
+        <v>-0.1766</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.2234</v>
+        <v>0.1853</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.8175</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.594</v>
+        <v>0.1853</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.011</v>
+        <v>0.0653</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.6414</v>
+        <v>-0.023</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6304</v>
+        <v>0.0883</v>
       </c>
       <c r="V21" t="n">
-        <v>2.8321</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.8316</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. PENAS REINO</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5805</v>
+        <v>-0.421</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.196</v>
+        <v>0.5948</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3845</v>
+        <v>-1.0158</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4062</v>
+        <v>-0.5986</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2095</v>
+        <v>-0.8002</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1967</v>
+        <v>0.2016</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0228</v>
+        <v>2.0052</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0429</v>
+        <v>1.8808</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0201</v>
+        <v>0.1244</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.429</v>
+        <v>-2.6038</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2524</v>
+        <v>-2.681</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1766</v>
+        <v>0.0772</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1853</v>
+        <v>2.0382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3596</v>
+        <v>0.1781</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2189</v>
+        <v>-0.3155</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1408</v>
+        <v>0.4937</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9784</v>
+        <v>-0.4635</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1367</v>
+        <v>-0.745</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1584</v>
+        <v>0.2815</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8439</v>
@@ -2248,13 +2248,13 @@
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4315</v>
+        <v>0.0833</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.383</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0485</v>
+        <v>0.0746</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6294</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3768</v>
+        <v>-2.0944</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7399</v>
+        <v>-2.8172</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3631</v>
+        <v>0.7228</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1017</v>
@@ -2326,13 +2326,13 @@
         <v>1.8529</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6514</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4266</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2248</v>
+        <v>0.5844</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T. GARRETT</t>
+          <t>S. VICENTE GARCIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2855</v>
+        <v>-4.6695</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.7892</v>
+        <v>-4.2151</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4963</v>
+        <v>-0.4544</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.0954</v>
+        <v>-5.0909</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.8697</v>
+        <v>-2.0972</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.2257</v>
+        <v>-2.9937</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.7326</v>
+        <v>-3.621</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4683</v>
+        <v>-0.4811</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2643</v>
+        <v>-3.1399</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3628</v>
+        <v>-1.47</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4014</v>
+        <v>-1.6161</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0386</v>
+        <v>0.1462</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.8529</v>
+        <v>-0.1853</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9264</v>
+        <v>1.8529</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2642</v>
+        <v>0.0127</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2037</v>
+        <v>-0.4088</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0605</v>
+        <v>0.4215</v>
       </c>
       <c r="V25" t="n">
-        <v>0.0005</v>
+        <v>-1.2589</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0005</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCIA</t>
+          <t>T. GARRETT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.7885</v>
+        <v>-4.9424</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.9006</v>
+        <v>-4.4954</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.8879</v>
+        <v>-0.447</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.0909</v>
+        <v>-3.0954</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.0972</v>
+        <v>-1.8697</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.9937</v>
+        <v>-1.2257</v>
       </c>
       <c r="J26" t="n">
-        <v>-3.621</v>
+        <v>-1.7326</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4811</v>
+        <v>-0.4683</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.1399</v>
+        <v>-1.2643</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.47</v>
+        <v>-1.3628</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.6161</v>
+        <v>-1.4014</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1462</v>
+        <v>0.0386</v>
       </c>
       <c r="P26" t="n">
-        <v>1.6676</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.1853</v>
+        <v>-1.8529</v>
       </c>
       <c r="R26" t="n">
-        <v>1.8529</v>
+        <v>0.9264</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.1063</v>
+        <v>-0.9211</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.0943</v>
+        <v>-0.9099</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.012</v>
+        <v>-0.0112</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.2589</v>
+        <v>0.0005</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2589</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-11.745</v>
+        <v>-10.4392</v>
       </c>
       <c r="E27" t="n">
-        <v>-11.4291</v>
+        <v>-11.4293</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3157</v>
+        <v>0.9901999999999997</v>
       </c>
       <c r="G27" t="n">
         <v>-14.0827</v>
@@ -2539,7 +2539,7 @@
         <v>3.0464</v>
       </c>
       <c r="L27" t="n">
-        <v>-5.4158</v>
+        <v>-5.415800000000001</v>
       </c>
       <c r="M27" t="n">
         <v>-11.7132</v>
@@ -2551,7 +2551,7 @@
         <v>1.6916</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.9263000000000001</v>
+        <v>-0.9262999999999998</v>
       </c>
       <c r="Q27" t="n">
         <v>-13.8967</v>
@@ -2560,13 +2560,13 @@
         <v>12.9702</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.4</v>
+        <v>-1.0942</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.9728</v>
+        <v>-3.9729</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5728</v>
+        <v>2.8786</v>
       </c>
       <c r="V27" t="n">
         <v>5.6642</v>
